--- a/assets/excel/Algorithmes/AttendanceSheet6.xlsx
+++ b/assets/excel/Algorithmes/AttendanceSheet6.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fci mobile project\Attendance\assets\excel\Algorithmes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nerme\Downloads\excel\Algorithmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9DD2EA-7703-4722-9374-4DB10C205748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11160"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXPORT_FACE_ATTENDANCE-20240818" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Name</t>
   </si>
@@ -36,91 +37,13 @@
     <t>Check In Time</t>
   </si>
   <si>
-    <t>18/08/2024</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Absenteeism</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>Late; Leave Early</t>
-  </si>
-  <si>
-    <t>احمد محمد ابراهيم محمد محمد</t>
-  </si>
-  <si>
-    <t>احمد هشام خيري شاكر</t>
-  </si>
-  <si>
-    <t>سيف محمد زايد محمد</t>
-  </si>
-  <si>
-    <t>علا محمد عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>معتصم بالله عبد العزيز محمود عبد العزيز</t>
-  </si>
-  <si>
-    <t>ديفيد باولينو تومبي جارا</t>
-  </si>
-  <si>
-    <t>ابانوب روماني وصفي شاكر حنين</t>
-  </si>
-  <si>
-    <t>ابانوب زكريا ابراهيم عبدالمسيح</t>
-  </si>
-  <si>
-    <t>ابتسام علي حادي محمود</t>
-  </si>
-  <si>
-    <t>ابراهيم محمد عبدالله عبدالعليم</t>
-  </si>
-  <si>
-    <t>احمد الحسن ابراهيم صادق</t>
-  </si>
-  <si>
-    <t>احمد جمال احمد ابراهيم ابوخطوه</t>
-  </si>
-  <si>
-    <t>احمد جمال عبدالظاهر محمد</t>
-  </si>
-  <si>
-    <t>احمد جمال علي جبيلي</t>
-  </si>
-  <si>
-    <t>احمد حسين احمد مصطفى</t>
-  </si>
-  <si>
-    <t>احمد درويش راشد درويش العوضي</t>
-  </si>
-  <si>
-    <t>احمد رضا عباس محمود محمد</t>
-  </si>
-  <si>
-    <t>احمد سليمان عبدالمنعم محمد</t>
-  </si>
-  <si>
-    <t>احمد سمير علي احمد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:3: AM; </t>
-  </si>
-  <si>
-    <t>09:35: AM</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -954,8 +877,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
@@ -982,387 +905,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>2021042</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>2023035</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4">
-        <v>2023105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>20220108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>20220175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>20220201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <v>20240001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>20240002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10">
-        <v>20240003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11">
-        <v>20240004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12">
-        <v>20240005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13">
-        <v>20240006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14">
-        <v>20240007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15">
-        <v>20240008</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16">
-        <v>20240009</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17">
-        <v>20240010</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18">
-        <v>20240011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19">
-        <v>20240012</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20">
-        <v>20240013</v>
       </c>
     </row>
   </sheetData>
